--- a/events/VilaVerde_2018_MAR/VilaVerde_2018_MAR_Results.xlsx
+++ b/events/VilaVerde_2018_MAR/VilaVerde_2018_MAR_Results.xlsx
@@ -22199,7 +22199,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>O’ROURKE Emily</t>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>O’ROURKE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/events/VilaVerde_2018_MAR/VilaVerde_2018_MAR_Results.xlsx
+++ b/events/VilaVerde_2018_MAR/VilaVerde_2018_MAR_Results.xlsx
@@ -1207,6 +1207,11 @@
           <t>01:37:40.790</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>85124</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1269,6 +1274,11 @@
           <t>01:37:41.660</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>71551</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1465,6 +1475,11 @@
           <t>01:38:59.260</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>130683</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2995,6 +3010,11 @@
           <t>01:12:06.990</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>75664</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5190,6 +5210,11 @@
           <t>01:39:22.890</t>
         </is>
       </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>76507</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8504,6 +8529,11 @@
           <t>87164</t>
         </is>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>98603</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8967,6 +8997,11 @@
           <t>01:54:54.080</t>
         </is>
       </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>71570</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9554,6 +9589,11 @@
           <t>01:35:15.460</t>
         </is>
       </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>76507</t>
+        </is>
+      </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>80679</t>
@@ -9914,6 +9954,11 @@
           <t>73771</t>
         </is>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>98702</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10264,6 +10309,11 @@
           <t>01:39:50.050</t>
         </is>
       </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>98038</t>
+        </is>
+      </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>87197</t>
@@ -12452,6 +12502,11 @@
           <t>02:07:46.770</t>
         </is>
       </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>79396</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -12700,6 +12755,11 @@
       <c r="N182" t="n">
         <v>28</v>
       </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>90342</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12751,6 +12811,11 @@
       <c r="L183" t="n">
         <v>197</v>
       </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>63925</t>
+        </is>
+      </c>
       <c r="X183" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -14202,6 +14267,11 @@
           <t>02:11:17.980</t>
         </is>
       </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14331,6 +14401,11 @@
           <t>02:13:09.220</t>
         </is>
       </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>135293</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -14527,6 +14602,11 @@
           <t>02:19:22.230</t>
         </is>
       </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -16320,6 +16400,11 @@
       <c r="L238" t="n">
         <v>293</v>
       </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
       <c r="X238" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -16637,6 +16722,11 @@
           <t>02:09:30.850</t>
         </is>
       </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -18039,6 +18129,11 @@
           <t>02:24:01.640</t>
         </is>
       </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>102896</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -18729,6 +18824,11 @@
           <t>63922</t>
         </is>
       </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>49654</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -19007,6 +19107,11 @@
           <t>01:59:52.380</t>
         </is>
       </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -19074,6 +19179,11 @@
           <t>48163</t>
         </is>
       </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>71570</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -19490,6 +19600,11 @@
           <t>36180</t>
         </is>
       </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
       <c r="X286" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -19845,6 +19960,11 @@
           <t>01:59:36.000</t>
         </is>
       </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
       <c r="S291" t="inlineStr">
         <is>
           <t>72831</t>
@@ -20620,6 +20740,11 @@
           <t>02:02:16.970</t>
         </is>
       </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
       <c r="S302" t="inlineStr">
         <is>
           <t>49664</t>
@@ -20764,6 +20889,11 @@
           <t>87418</t>
         </is>
       </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>87419</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -20970,6 +21100,11 @@
           <t>02:02:56.680</t>
         </is>
       </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>63429</t>
+        </is>
+      </c>
       <c r="S307" t="inlineStr">
         <is>
           <t>70640</t>
@@ -21745,6 +21880,11 @@
       <c r="P318" t="inlineStr">
         <is>
           <t>02:11:20.630</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>47481</t>
         </is>
       </c>
       <c r="S318" t="inlineStr">
@@ -22166,7 +22306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D295"/>
+  <dimension ref="A1:D317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28659,6 +28799,490 @@
         </is>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Joana</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>SOUSA</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>47481</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>CAFFA</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>49654</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Levente</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>BALLA</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>BOROS</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>ERLINEKOV</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>BARROS</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>63429</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Marton</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>MESZAROS</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>63925</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Mate</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>GYORGJAKAB</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>71551</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>GOMES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>71570</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>COELHO</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>75664</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>RODRIGUES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>76507</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Thorbjorn</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>RASK</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>79396</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Mihai-Denis</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>SERBAN</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>85124</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>ROEHLINGS</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>87419</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>FERNANDEZ CASTANON</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>90342</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Keiichi</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>YAMAGUCHI</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>98038</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>CASTRO SILVA</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>98603</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>REGO GOMES</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>98702</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>FENN</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>102896</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>SADA</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>130683</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Ardis</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>LUDA</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>135293</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Gergely</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>NAGY</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/VilaVerde_2018_MAR/VilaVerde_2018_MAR_Results.xlsx
+++ b/events/VilaVerde_2018_MAR/VilaVerde_2018_MAR_Results.xlsx
@@ -15377,6 +15377,11 @@
           <t>02:07:08.730</t>
         </is>
       </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -22306,7 +22311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D317"/>
+  <dimension ref="A1:D318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29283,6 +29288,28 @@
         </is>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Kristina</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>BEDEC</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
